--- a/2024-09-20018D Source Data Ext. Fig. 10.xlsx
+++ b/2024-09-20018D Source Data Ext. Fig. 10.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10413"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ytian\Desktop\Source Data_Clean_KNIT\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hw/hfgwang drive/学生总结/郜艳敏/KNIT version/B. 2024-09-20018D KNIT editing All /Updated KE files 2024-09-20018D /KE Source Data Excels (updated KE version)/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAAD6D46-270E-4FB5-B50C-7FEE0EC7F514}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C43AF70A-43CA-EA4B-91BD-17DA8679E3D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3800" yWindow="2420" windowWidth="21800" windowHeight="12980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ext. Fig. 10a" sheetId="21" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="45">
   <si>
     <t>Ext. Fig. 10a</t>
   </si>
@@ -89,9 +89,6 @@
   </si>
   <si>
     <t>Ext. Fig. 10j</t>
-  </si>
-  <si>
-    <t>enIE(RNP)</t>
   </si>
   <si>
     <t>Ext. Fig. 10k (left)</t>
@@ -245,23 +242,32 @@
     <t>KE</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
+  <si>
+    <t>KE1 (RNP)</t>
+  </si>
+  <si>
+    <t>KE2 (mRNA)</t>
+  </si>
+  <si>
+    <t>KE1 (mRNA)</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="0.0%"/>
-    <numFmt numFmtId="177" formatCode="0.0_ "/>
-    <numFmt numFmtId="178" formatCode="0.000_ "/>
-    <numFmt numFmtId="179" formatCode="0.000%"/>
-    <numFmt numFmtId="180" formatCode="0.00_);[Red]\(0.00\)"/>
+    <numFmt numFmtId="164" formatCode="0.0%"/>
+    <numFmt numFmtId="165" formatCode="0.0_ "/>
+    <numFmt numFmtId="166" formatCode="0.000_ "/>
+    <numFmt numFmtId="167" formatCode="0.000%"/>
+    <numFmt numFmtId="168" formatCode="0.00_);[Red]\(0.00\)"/>
   </numFmts>
   <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -304,7 +310,7 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="等线"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -312,7 +318,7 @@
     <font>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -438,19 +444,19 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="177" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="177" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="178" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="10" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="180" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="168" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="1" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="176" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="164" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="10" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
@@ -465,7 +471,7 @@
     <xf numFmtId="10" fontId="4" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="165" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -477,7 +483,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="常规 2" xfId="1" xr:uid="{240A3C0D-A41B-410E-87D8-EF9B3DF387C9}"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -752,27 +758,27 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="17.17578125" customWidth="1"/>
-    <col min="2" max="2" width="20.46875" customWidth="1"/>
-    <col min="3" max="3" width="22.46875" customWidth="1"/>
+    <col min="1" max="1" width="17.1640625" customWidth="1"/>
+    <col min="2" max="2" width="20.5" customWidth="1"/>
+    <col min="3" max="3" width="22.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.4">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" s="12">
         <v>11.43</v>
       </c>
@@ -780,7 +786,7 @@
         <v>11.24</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" s="12">
         <v>12.56</v>
       </c>
@@ -788,7 +794,7 @@
         <v>9.77</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" s="12">
         <v>9.48</v>
       </c>
@@ -805,19 +811,19 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:G109"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="18.46875" customWidth="1"/>
-    <col min="2" max="2" width="20.46875" customWidth="1"/>
-    <col min="3" max="3" width="22.46875" customWidth="1"/>
+    <col min="1" max="1" width="18.5" customWidth="1"/>
+    <col min="2" max="2" width="20.5" customWidth="1"/>
+    <col min="3" max="3" width="22.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:7" ht="17" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.4">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" s="6"/>
       <c r="B2" s="28" t="s">
         <v>1</v>
@@ -825,14 +831,14 @@
       <c r="C2" s="28"/>
       <c r="D2" s="28"/>
       <c r="E2" s="28" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F2" s="28"/>
       <c r="G2" s="28"/>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" s="6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B3" s="20">
         <v>1.6E-2</v>
@@ -853,9 +859,9 @@
         <v>1E-4</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" s="6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B4" s="21">
         <v>3.0999999999999999E-3</v>
@@ -876,9 +882,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" s="6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B5" s="22">
         <v>0</v>
@@ -899,7 +905,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="108" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A108">
         <v>79.599999999999994</v>
       </c>
@@ -910,7 +916,7 @@
         <v>46.6</v>
       </c>
     </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="109" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A109">
         <v>78.599999999999994</v>
       </c>
@@ -934,19 +940,19 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:G14"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="17.17578125" customWidth="1"/>
-    <col min="2" max="2" width="20.46875" customWidth="1"/>
-    <col min="3" max="3" width="22.46875" customWidth="1"/>
+    <col min="1" max="1" width="17.1640625" customWidth="1"/>
+    <col min="2" max="2" width="20.5" customWidth="1"/>
+    <col min="3" max="3" width="22.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:7" ht="17" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.4">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" s="6"/>
       <c r="B2" s="28" t="s">
         <v>1</v>
@@ -954,14 +960,14 @@
       <c r="C2" s="28"/>
       <c r="D2" s="28"/>
       <c r="E2" s="28" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F2" s="28"/>
       <c r="G2" s="28"/>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" s="6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B3" s="16">
         <v>1.534E-3</v>
@@ -982,9 +988,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B4" s="16">
         <v>2.3700000000000001E-3</v>
@@ -1005,9 +1011,9 @@
         <v>2.0000000000000001E-4</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B5" s="16">
         <v>2.3700000000000001E-3</v>
@@ -1028,9 +1034,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" s="6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B6" s="16">
         <v>2.928E-3</v>
@@ -1051,16 +1057,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="F11" s="15"/>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="F12" s="15"/>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="F13" s="15"/>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="F14" s="15"/>
     </row>
   </sheetData>
@@ -1076,30 +1082,30 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="17.17578125" customWidth="1"/>
-    <col min="2" max="2" width="20.46875" customWidth="1"/>
-    <col min="3" max="3" width="22.46875" customWidth="1"/>
+    <col min="1" max="1" width="17.1640625" customWidth="1"/>
+    <col min="2" max="2" width="20.5" customWidth="1"/>
+    <col min="3" max="3" width="22.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" s="13">
         <v>0.93</v>
       </c>
@@ -1110,7 +1116,7 @@
         <v>4.32</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" s="13">
         <v>1.26</v>
       </c>
@@ -1121,7 +1127,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" s="13">
         <v>0.81</v>
       </c>
@@ -1141,24 +1147,24 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <dimension ref="A1:AT15"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="17.17578125" customWidth="1"/>
-    <col min="2" max="2" width="20.46875" customWidth="1"/>
-    <col min="3" max="3" width="22.46875" customWidth="1"/>
+    <col min="1" max="1" width="17.1640625" customWidth="1"/>
+    <col min="2" max="2" width="20.5" customWidth="1"/>
+    <col min="3" max="3" width="22.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:46" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:46" ht="17" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="2" spans="1:46" x14ac:dyDescent="0.2">
+      <c r="A2" s="4" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="2" spans="1:46" ht="15.4" x14ac:dyDescent="0.4">
-      <c r="A2" s="4" t="s">
+      <c r="B2" s="28" t="s">
         <v>30</v>
-      </c>
-      <c r="B2" s="28" t="s">
-        <v>31</v>
       </c>
       <c r="C2" s="28"/>
       <c r="D2" s="28"/>
@@ -1169,7 +1175,7 @@
       <c r="I2" s="28"/>
       <c r="J2" s="28"/>
       <c r="K2" s="28" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="L2" s="28"/>
       <c r="M2" s="28"/>
@@ -1180,7 +1186,7 @@
       <c r="R2" s="28"/>
       <c r="S2" s="28"/>
       <c r="T2" s="28" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="U2" s="28"/>
       <c r="V2" s="28"/>
@@ -1191,7 +1197,7 @@
       <c r="AA2" s="28"/>
       <c r="AB2" s="28"/>
       <c r="AC2" s="28" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="AD2" s="28"/>
       <c r="AE2" s="28"/>
@@ -1202,7 +1208,7 @@
       <c r="AJ2" s="28"/>
       <c r="AK2" s="28"/>
       <c r="AL2" s="28" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AM2" s="28"/>
       <c r="AN2" s="28"/>
@@ -1213,7 +1219,7 @@
       <c r="AS2" s="28"/>
       <c r="AT2" s="28"/>
     </row>
-    <row r="3" spans="1:46" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:46" x14ac:dyDescent="0.2">
       <c r="A3" s="3">
         <v>0</v>
       </c>
@@ -1353,7 +1359,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:46" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:46" x14ac:dyDescent="0.2">
       <c r="A4" s="3">
         <v>2</v>
       </c>
@@ -1493,7 +1499,7 @@
         <v>1.0833930000000001</v>
       </c>
     </row>
-    <row r="5" spans="1:46" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:46" x14ac:dyDescent="0.2">
       <c r="A5" s="3">
         <v>4</v>
       </c>
@@ -1633,7 +1639,7 @@
         <v>1.1762900000000001</v>
       </c>
     </row>
-    <row r="6" spans="1:46" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:46" x14ac:dyDescent="0.2">
       <c r="A6" s="3">
         <v>6</v>
       </c>
@@ -1773,7 +1779,7 @@
         <v>1.274662</v>
       </c>
     </row>
-    <row r="7" spans="1:46" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:46" x14ac:dyDescent="0.2">
       <c r="A7" s="3">
         <v>8</v>
       </c>
@@ -1913,7 +1919,7 @@
         <v>1.3822570000000001</v>
       </c>
     </row>
-    <row r="8" spans="1:46" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:46" x14ac:dyDescent="0.2">
       <c r="A8" s="3">
         <v>10</v>
       </c>
@@ -2053,7 +2059,7 @@
         <v>1.5175209999999999</v>
       </c>
     </row>
-    <row r="9" spans="1:46" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:46" x14ac:dyDescent="0.2">
       <c r="A9" s="3">
         <v>12</v>
       </c>
@@ -2193,7 +2199,7 @@
         <v>1.6403179999999999</v>
       </c>
     </row>
-    <row r="10" spans="1:46" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:46" x14ac:dyDescent="0.2">
       <c r="A10" s="3">
         <v>14</v>
       </c>
@@ -2333,7 +2339,7 @@
         <v>1.7943260000000001</v>
       </c>
     </row>
-    <row r="11" spans="1:46" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:46" x14ac:dyDescent="0.2">
       <c r="A11" s="3">
         <v>16</v>
       </c>
@@ -2473,7 +2479,7 @@
         <v>1.946887</v>
       </c>
     </row>
-    <row r="12" spans="1:46" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:46" x14ac:dyDescent="0.2">
       <c r="A12" s="3">
         <v>18</v>
       </c>
@@ -2613,7 +2619,7 @@
         <v>2.13672</v>
       </c>
     </row>
-    <row r="13" spans="1:46" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:46" x14ac:dyDescent="0.2">
       <c r="A13" s="3">
         <v>20</v>
       </c>
@@ -2753,7 +2759,7 @@
         <v>2.301599</v>
       </c>
     </row>
-    <row r="14" spans="1:46" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:46" x14ac:dyDescent="0.2">
       <c r="A14" s="3">
         <v>22</v>
       </c>
@@ -2893,7 +2899,7 @@
         <v>2.5153279999999998</v>
       </c>
     </row>
-    <row r="15" spans="1:46" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:46" x14ac:dyDescent="0.2">
       <c r="A15" s="3">
         <v>24</v>
       </c>
@@ -3049,30 +3055,30 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="17.17578125" customWidth="1"/>
-    <col min="2" max="2" width="20.46875" customWidth="1"/>
-    <col min="3" max="3" width="22.46875" customWidth="1"/>
+    <col min="1" max="1" width="17.1640625" customWidth="1"/>
+    <col min="2" max="2" width="20.5" customWidth="1"/>
+    <col min="3" max="3" width="22.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2" s="2" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="A2" s="2" t="s">
+      <c r="B2" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C2" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" s="25">
         <v>85.5</v>
       </c>
@@ -3083,7 +3089,7 @@
         <v>50.8</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" s="25">
         <v>79.599999999999994</v>
       </c>
@@ -3094,7 +3100,7 @@
         <v>46.6</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" s="25">
         <v>78</v>
       </c>
@@ -3114,19 +3120,19 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:E6"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="17.17578125" customWidth="1"/>
-    <col min="2" max="2" width="20.46875" customWidth="1"/>
-    <col min="3" max="3" width="22.46875" customWidth="1"/>
+    <col min="1" max="1" width="17.1640625" customWidth="1"/>
+    <col min="2" max="2" width="20.5" customWidth="1"/>
+    <col min="3" max="3" width="22.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:5" ht="17" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" s="26" t="s">
         <v>3</v>
       </c>
@@ -3136,21 +3142,21 @@
       </c>
       <c r="E2" s="27"/>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
         <v>1</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D3" s="5" t="s">
         <v>1</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.4">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" s="3">
         <v>20950</v>
       </c>
@@ -3164,7 +3170,7 @@
         <v>14650</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" s="3">
         <v>25050</v>
       </c>
@@ -3178,7 +3184,7 @@
         <v>10705</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" s="3">
         <v>21550</v>
       </c>
@@ -3205,19 +3211,19 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="17.17578125" customWidth="1"/>
-    <col min="2" max="2" width="20.46875" customWidth="1"/>
-    <col min="3" max="3" width="22.46875" customWidth="1"/>
+    <col min="1" max="1" width="17.1640625" customWidth="1"/>
+    <col min="2" max="2" width="20.5" customWidth="1"/>
+    <col min="3" max="3" width="22.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" ht="34" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>6</v>
       </c>
@@ -3228,7 +3234,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" s="17">
         <v>98.9</v>
       </c>
@@ -3239,7 +3245,7 @@
         <v>99.4</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" s="17">
         <v>99</v>
       </c>
@@ -3250,7 +3256,7 @@
         <v>99.5</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" s="17">
         <v>99.2</v>
       </c>
@@ -3270,27 +3276,27 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="17.17578125" customWidth="1"/>
-    <col min="2" max="2" width="20.46875" customWidth="1"/>
-    <col min="3" max="3" width="22.46875" customWidth="1"/>
+    <col min="1" max="1" width="17.1640625" customWidth="1"/>
+    <col min="2" max="2" width="20.5" customWidth="1"/>
+    <col min="3" max="3" width="22.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.4">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" s="18">
         <v>59.33</v>
       </c>
@@ -3298,7 +3304,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" s="18">
         <v>28.17</v>
       </c>
@@ -3306,7 +3312,7 @@
         <v>1.35</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" s="18">
         <v>35.01</v>
       </c>
@@ -3324,27 +3330,27 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="17.17578125" customWidth="1"/>
-    <col min="2" max="2" width="20.46875" customWidth="1"/>
-    <col min="3" max="3" width="22.46875" customWidth="1"/>
+    <col min="1" max="1" width="17.1640625" customWidth="1"/>
+    <col min="2" max="2" width="20.5" customWidth="1"/>
+    <col min="3" max="3" width="22.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.4">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" s="3">
         <v>1.4</v>
       </c>
@@ -3352,7 +3358,7 @@
         <v>0.27</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" s="3">
         <v>0.85</v>
       </c>
@@ -3360,7 +3366,7 @@
         <v>0.16</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" s="3">
         <v>0.75</v>
       </c>
@@ -3377,27 +3383,27 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="17.17578125" customWidth="1"/>
-    <col min="2" max="2" width="20.46875" customWidth="1"/>
-    <col min="3" max="3" width="22.46875" customWidth="1"/>
+    <col min="1" max="1" width="17.1640625" customWidth="1"/>
+    <col min="2" max="2" width="20.5" customWidth="1"/>
+    <col min="3" max="3" width="22.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" s="6" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.4">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" s="3">
         <v>1.1599999999999999</v>
       </c>
@@ -3405,7 +3411,7 @@
         <v>0.54</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" s="3">
         <v>1.1299999999999999</v>
       </c>
@@ -3413,7 +3419,7 @@
         <v>0.55000000000000004</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" s="3">
         <v>0.71</v>
       </c>
@@ -3431,19 +3437,19 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:F109"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="17.17578125" customWidth="1"/>
-    <col min="2" max="2" width="20.46875" customWidth="1"/>
-    <col min="3" max="3" width="22.46875" customWidth="1"/>
+    <col min="1" max="1" width="17.1640625" customWidth="1"/>
+    <col min="2" max="2" width="20.5" customWidth="1"/>
+    <col min="3" max="3" width="22.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:5" ht="17" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" s="26" t="s">
         <v>3</v>
       </c>
@@ -3454,22 +3460,22 @@
       </c>
       <c r="E2" s="27"/>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C3" s="9"/>
       <c r="D3" s="2" t="s">
         <v>1</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.4">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" s="3">
         <v>15100</v>
       </c>
@@ -3484,7 +3490,7 @@
         <v>42950</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" s="3">
         <v>30350</v>
       </c>
@@ -3499,7 +3505,7 @@
         <v>43700</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" s="3">
         <v>34100</v>
       </c>
@@ -3514,24 +3520,24 @@
         <v>25100</v>
       </c>
     </row>
-    <row r="45" spans="6:6" x14ac:dyDescent="0.4">
+    <row r="45" spans="6:6" x14ac:dyDescent="0.2">
       <c r="F45" s="9"/>
     </row>
-    <row r="46" spans="6:6" x14ac:dyDescent="0.4">
+    <row r="46" spans="6:6" x14ac:dyDescent="0.2">
       <c r="F46" s="10"/>
     </row>
-    <row r="47" spans="6:6" x14ac:dyDescent="0.4">
+    <row r="47" spans="6:6" x14ac:dyDescent="0.2">
       <c r="F47" s="11"/>
     </row>
-    <row r="48" spans="6:6" x14ac:dyDescent="0.4">
+    <row r="48" spans="6:6" x14ac:dyDescent="0.2">
       <c r="F48" s="11"/>
     </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="108" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A108" s="3"/>
       <c r="B108" s="3"/>
       <c r="C108" s="3"/>
     </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="109" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A109" s="3"/>
       <c r="B109" s="3"/>
       <c r="C109" s="3"/>
@@ -3549,30 +3555,30 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="17.17578125" customWidth="1"/>
-    <col min="2" max="2" width="20.46875" customWidth="1"/>
-    <col min="3" max="3" width="22.46875" customWidth="1"/>
+    <col min="1" max="1" width="17.1640625" customWidth="1"/>
+    <col min="2" max="2" width="20.5" customWidth="1"/>
+    <col min="3" max="3" width="22.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
-        <v>15</v>
+        <v>42</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" s="3">
         <v>32500</v>
       </c>
@@ -3583,7 +3589,7 @@
         <v>88850</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" s="3">
         <v>48400</v>
       </c>
@@ -3594,7 +3600,7 @@
         <v>71230</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" s="3">
         <v>28200</v>
       </c>
@@ -3614,27 +3620,27 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="17.17578125" customWidth="1"/>
-    <col min="2" max="2" width="20.46875" customWidth="1"/>
-    <col min="3" max="3" width="22.46875" customWidth="1"/>
+    <col min="1" max="1" width="17.1640625" customWidth="1"/>
+    <col min="2" max="2" width="20.5" customWidth="1"/>
+    <col min="3" max="3" width="22.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:2" ht="34" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A2" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A2" s="3" t="s">
+      <c r="B2" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.4">
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" s="17">
         <v>99.3</v>
       </c>
@@ -3642,7 +3648,7 @@
         <v>99.4</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" s="17">
         <v>99.4</v>
       </c>
@@ -3650,7 +3656,7 @@
         <v>99.5</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" s="17">
         <v>99.4</v>
       </c>

--- a/2024-09-20018D Source Data Ext. Fig. 10.xlsx
+++ b/2024-09-20018D Source Data Ext. Fig. 10.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hw/hfgwang drive/学生总结/郜艳敏/KNIT version/B. 2024-09-20018D KNIT editing All /Updated KE files 2024-09-20018D /KE Source Data Excels (updated KE version)/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hw/hfgwang drive/学生总结/郜艳敏/KNIT version/google drive KE version/older files/B. 2024-09-20018D KNIT editing All /Updated KE files 2024-09-20018D /KE Source Data Excels (updated KE version)/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C43AF70A-43CA-EA4B-91BD-17DA8679E3D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3800828-7EC5-FB49-B6FE-2C09F94A81D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3800" yWindow="2420" windowWidth="21800" windowHeight="12980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="80" yWindow="1700" windowWidth="21800" windowHeight="12980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ext. Fig. 10a" sheetId="21" r:id="rId1"/>
@@ -810,7 +810,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
-  <dimension ref="A1:G109"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="18.5" customWidth="1"/>
@@ -903,28 +903,6 @@
       </c>
       <c r="G5" s="8">
         <v>0</v>
-      </c>
-    </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A108">
-        <v>79.599999999999994</v>
-      </c>
-      <c r="B108">
-        <v>61.4</v>
-      </c>
-      <c r="C108">
-        <v>46.6</v>
-      </c>
-    </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A109">
-        <v>78.599999999999994</v>
-      </c>
-      <c r="B109">
-        <v>60.5</v>
-      </c>
-      <c r="C109">
-        <v>47.5</v>
       </c>
     </row>
   </sheetData>

--- a/2024-09-20018D Source Data Ext. Fig. 10.xlsx
+++ b/2024-09-20018D Source Data Ext. Fig. 10.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hw/hfgwang drive/学生总结/郜艳敏/KNIT version/google drive KE version/older files/B. 2024-09-20018D KNIT editing All /Updated KE files 2024-09-20018D /KE Source Data Excels (updated KE version)/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hw/hfgwang drive/学生总结/郜艳敏/KNIT version/B. 2024-09-20018D KNIT editing All /Updated KE files 2024-09-20018D /KE Source Data Excels (updated KE version)/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3800828-7EC5-FB49-B6FE-2C09F94A81D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C43AF70A-43CA-EA4B-91BD-17DA8679E3D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="80" yWindow="1700" windowWidth="21800" windowHeight="12980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3800" yWindow="2420" windowWidth="21800" windowHeight="12980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ext. Fig. 10a" sheetId="21" r:id="rId1"/>
@@ -810,7 +810,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G109"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="18.5" customWidth="1"/>
@@ -903,6 +903,28 @@
       </c>
       <c r="G5" s="8">
         <v>0</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A108">
+        <v>79.599999999999994</v>
+      </c>
+      <c r="B108">
+        <v>61.4</v>
+      </c>
+      <c r="C108">
+        <v>46.6</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A109">
+        <v>78.599999999999994</v>
+      </c>
+      <c r="B109">
+        <v>60.5</v>
+      </c>
+      <c r="C109">
+        <v>47.5</v>
       </c>
     </row>
   </sheetData>
@@ -3646,4 +3668,262 @@
   <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101002A580DDD6E32D24793B52EBDA382135E" ma:contentTypeVersion="24" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="420b5df69e2a8ef095a347c37071042d">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="03670651-1d3f-4393-a695-0ad38e7dc27c" xmlns:ns3="98cfd510-5244-40a7-ac81-0d7d1b58424e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="43051459d3b7bcd6c9644565fa79aaf6" ns2:_="" ns3:_="">
+    <xsd:import namespace="03670651-1d3f-4393-a695-0ad38e7dc27c"/>
+    <xsd:import namespace="98cfd510-5244-40a7-ac81-0d7d1b58424e"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MigrationSourceID" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns3:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns2:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceLocation" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceBillingMetadata" minOccurs="0"/>
+                <xsd:element ref="ns3:ArchiverLinkFileType" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="03670651-1d3f-4393-a695-0ad38e7dc27c" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MigrationSourceID" ma:index="8" nillable="true" ma:displayName="MigrationSourceID" ma:internalName="MigrationSourceID" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="TaxCatchAll" ma:index="19" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{fe026092-a6d1-42a7-a35d-9d1bdd270ae7}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="03670651-1d3f-4393-a695-0ad38e7dc27c">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="98cfd510-5244-40a7-ac81-0d7d1b58424e" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="10" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="11" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="12" nillable="true" ma:displayName="MediaServiceDateTaken" ma:description="" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="13" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:description="" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="16" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="18" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="4fb58666-e629-4e5a-b780-b8dcc15b318b" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="20" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="21" nillable="true" ma:displayName="Location" ma:description="" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceBillingMetadata" ma:index="22" nillable="true" ma:displayName="MediaServiceBillingMetadata" ma:hidden="true" ma:internalName="MediaServiceBillingMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="ArchiverLinkFileType" ma:index="23" nillable="true" ma:displayName="ArchiverLinkFileType" ma:hidden="true" ma:internalName="ArchiverLinkFileType">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="03670651-1d3f-4393-a695-0ad38e7dc27c" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="98cfd510-5244-40a7-ac81-0d7d1b58424e">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <ArchiverLinkFileType xmlns="98cfd510-5244-40a7-ac81-0d7d1b58424e" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{95A32CE4-5B86-4E1D-8EC5-053A196E1300}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C692CE56-706C-405D-8DCB-790B9631886C}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6968762-C4D1-460C-8571-1A4FC5282C2C}"/>
 </file>